--- a/config/acquisitionConfig/roi.csv.xlsx
+++ b/config/acquisitionConfig/roi.csv.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Work\MuscleMuseum\config\acquisitionConfig\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scientist\Documents\MMUser\config\acquisitionConfig\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B580871-9AF1-48FA-B01E-79EC7F4EECF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D14D9A-7459-4CAB-A3E7-5899F804AB94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
   <si>
     <t>Angle</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -74,31 +74,31 @@
     <t>[]</t>
   </si>
   <si>
-    <t>[1 1]</t>
-  </si>
-  <si>
-    <t>[100 100]</t>
-  </si>
-  <si>
     <t>Test</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test2</t>
+  </si>
+  <si>
+    <t>ODT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -128,7 +128,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -406,23 +406,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="25.86328125" customWidth="1"/>
-    <col min="2" max="5" width="5.1328125" customWidth="1"/>
-    <col min="6" max="6" width="11.1328125" customWidth="1"/>
-    <col min="7" max="7" width="11.265625" customWidth="1"/>
-    <col min="8" max="8" width="6.265625" customWidth="1"/>
-    <col min="9" max="9" width="75.265625" customWidth="1"/>
-    <col min="10" max="10" width="19.3984375" customWidth="1"/>
-    <col min="11" max="11" width="16.86328125" customWidth="1"/>
-    <col min="12" max="12" width="3.1328125" customWidth="1"/>
-    <col min="13" max="14" width="2.1328125" customWidth="1"/>
-    <col min="15" max="16" width="4.1328125" customWidth="1"/>
+    <col min="1" max="1" width="6.42578125" customWidth="1"/>
+    <col min="2" max="2" width="3.140625" customWidth="1"/>
+    <col min="3" max="3" width="5.140625" customWidth="1"/>
+    <col min="4" max="4" width="4.140625" customWidth="1"/>
+    <col min="5" max="5" width="5.140625" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" customWidth="1"/>
+    <col min="8" max="8" width="6.28515625" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" customWidth="1"/>
+    <col min="11" max="11" width="16.85546875" customWidth="1"/>
+    <col min="12" max="12" width="3.140625" customWidth="1"/>
+    <col min="13" max="14" width="2.140625" customWidth="1"/>
+    <col min="15" max="16" width="4.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -457,9 +460,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -486,10 +489,80 @@
         <v>11</v>
       </c>
       <c r="J2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
         <v>13</v>
+      </c>
+      <c r="B3">
+        <v>90</v>
+      </c>
+      <c r="C3">
+        <v>436</v>
+      </c>
+      <c r="D3">
+        <v>126</v>
+      </c>
+      <c r="E3">
+        <v>400</v>
+      </c>
+      <c r="F3">
+        <v>512</v>
+      </c>
+      <c r="G3">
+        <v>512</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>85</v>
+      </c>
+      <c r="C4">
+        <v>440</v>
+      </c>
+      <c r="D4">
+        <v>80</v>
+      </c>
+      <c r="E4">
+        <v>435</v>
+      </c>
+      <c r="F4">
+        <v>512</v>
+      </c>
+      <c r="G4">
+        <v>512</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/config/acquisitionConfig/roi.csv.xlsx
+++ b/config/acquisitionConfig/roi.csv.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="585">
   <si>
     <t>Angle</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1579,6 +1579,222 @@
   </si>
   <si>
     <t>[100 100]</t>
+  </si>
+  <si>
+    <t>NILatticeKd</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeBoBmTof5000</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeBoBmTof5000</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeDepthCalibTof6000</t>
+  </si>
+  <si>
+    <t>[985 1253 130 100]</t>
+  </si>
+  <si>
+    <t>[3 1]</t>
+  </si>
+  <si>
+    <t>[270 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeDepthCalibTof6000</t>
+  </si>
+  <si>
+    <t>[985 1253 130 100]</t>
+  </si>
+  <si>
+    <t>[3 1]</t>
+  </si>
+  <si>
+    <t>[270 100]</t>
+  </si>
+  <si>
+    <t>BMPDloopTof6000</t>
+  </si>
+  <si>
+    <t>[909 1252 200 100]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[800 100]</t>
+  </si>
+  <si>
+    <t>BMPDloopTof8000</t>
+  </si>
+  <si>
+    <t>[984 1251 130 100]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[1000 100]</t>
+  </si>
+  <si>
+    <t>BMPDloopTof8000</t>
+  </si>
+  <si>
+    <t>[984 1251 160 100]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[950 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeDepthCalibTof8000</t>
+  </si>
+  <si>
+    <t>[985 1251 100 80]</t>
+  </si>
+  <si>
+    <t>[3 1]</t>
+  </si>
+  <si>
+    <t>[340 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeDepthCalibTof8000</t>
+  </si>
+  <si>
+    <t>[985 1251 100 80]</t>
+  </si>
+  <si>
+    <t>[3 1]</t>
+  </si>
+  <si>
+    <t>[340 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeDepthCalibTof8000</t>
+  </si>
+  <si>
+    <t>[985 1251 140 100]</t>
+  </si>
+  <si>
+    <t>[3 1]</t>
+  </si>
+  <si>
+    <t>[440 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeDepthCalibTof8000</t>
+  </si>
+  <si>
+    <t>[985 1251 140 130]</t>
+  </si>
+  <si>
+    <t>[3 1]</t>
+  </si>
+  <si>
+    <t>[440 100]</t>
+  </si>
+  <si>
+    <t>Bec</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>NILatticeKd</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeDepthCalibTof8000</t>
+  </si>
+  <si>
+    <t>[985 1251 140 130]</t>
+  </si>
+  <si>
+    <t>[3 1]</t>
+  </si>
+  <si>
+    <t>[440 100]</t>
+  </si>
+  <si>
+    <t>BMPDloopTof8000</t>
+  </si>
+  <si>
+    <t>[985 1261 160 120]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[950 100]</t>
+  </si>
+  <si>
+    <t>BMPDloopTof8000</t>
+  </si>
+  <si>
+    <t>[949 1263 160 120]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[950 100]</t>
+  </si>
+  <si>
+    <t>BMPDloopTof8000</t>
+  </si>
+  <si>
+    <t>[949 1263 160 120]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[950 100]</t>
   </si>
 </sst>
 </file>
@@ -2060,19 +2276,19 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>489</v>
+        <v>561</v>
       </c>
       <c r="B5" s="0">
-        <v>896</v>
+        <v>865</v>
       </c>
       <c r="C5" s="0">
-        <v>1182</v>
+        <v>1135</v>
       </c>
       <c r="D5" s="0">
-        <v>1161</v>
+        <v>1145</v>
       </c>
       <c r="E5" s="0">
-        <v>1453</v>
+        <v>1447</v>
       </c>
       <c r="F5" s="0">
         <v>2160</v>
@@ -2084,13 +2300,13 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>490</v>
+        <v>562</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>491</v>
+        <v>563</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>492</v>
+        <v>564</v>
       </c>
     </row>
     <row r="6">
@@ -2165,19 +2381,19 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>377</v>
+        <v>565</v>
       </c>
       <c r="B8" s="0">
-        <v>708</v>
+        <v>644</v>
       </c>
       <c r="C8" s="0">
         <v>1400</v>
       </c>
       <c r="D8" s="0">
-        <v>1346</v>
+        <v>1244</v>
       </c>
       <c r="E8" s="0">
-        <v>1400</v>
+        <v>1354</v>
       </c>
       <c r="F8" s="0">
         <v>2160</v>
@@ -2189,13 +2405,13 @@
         <v>2.3000000000000003</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>378</v>
+        <v>566</v>
       </c>
       <c r="J8" s="0" t="s">
-        <v>379</v>
+        <v>567</v>
       </c>
       <c r="K8" s="0" t="s">
-        <v>380</v>
+        <v>568</v>
       </c>
     </row>
     <row r="9">
@@ -2655,19 +2871,19 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>481</v>
+        <v>581</v>
       </c>
       <c r="B22" s="0">
-        <v>463</v>
+        <v>406</v>
       </c>
       <c r="C22" s="0">
-        <v>1645</v>
+        <v>1726</v>
       </c>
       <c r="D22" s="0">
-        <v>1476</v>
+        <v>1182</v>
       </c>
       <c r="E22" s="0">
-        <v>1596</v>
+        <v>1412</v>
       </c>
       <c r="F22" s="0">
         <v>2160</v>
@@ -2679,30 +2895,30 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>482</v>
+        <v>582</v>
       </c>
       <c r="J22" s="0" t="s">
-        <v>483</v>
+        <v>583</v>
       </c>
       <c r="K22" s="0" t="s">
-        <v>484</v>
+        <v>584</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>193</v>
+        <v>569</v>
       </c>
       <c r="B23" s="0">
-        <v>747</v>
+        <v>468</v>
       </c>
       <c r="C23" s="0">
-        <v>1801</v>
+        <v>1648</v>
       </c>
       <c r="D23" s="0">
-        <v>1440</v>
+        <v>1046</v>
       </c>
       <c r="E23" s="0">
-        <v>1724</v>
+        <v>1558</v>
       </c>
       <c r="F23" s="0">
         <v>2160</v>
@@ -2711,16 +2927,16 @@
         <v>2560</v>
       </c>
       <c r="H23" s="0">
-        <v>349.10000000000002</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>194</v>
+        <v>570</v>
       </c>
       <c r="J23" s="0" t="s">
-        <v>195</v>
+        <v>571</v>
       </c>
       <c r="K23" s="0" t="s">
-        <v>196</v>
+        <v>572</v>
       </c>
     </row>
     <row r="24">
@@ -2795,19 +3011,19 @@
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>413</v>
+        <v>529</v>
       </c>
       <c r="B26" s="0">
-        <v>634</v>
+        <v>618</v>
       </c>
       <c r="C26" s="0">
-        <v>1422</v>
+        <v>1488</v>
       </c>
       <c r="D26" s="0">
-        <v>1333</v>
+        <v>1150</v>
       </c>
       <c r="E26" s="0">
-        <v>1563</v>
+        <v>1458</v>
       </c>
       <c r="F26" s="0">
         <v>2160</v>
@@ -2819,13 +3035,13 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>414</v>
+        <v>530</v>
       </c>
       <c r="J26" s="0" t="s">
-        <v>415</v>
+        <v>531</v>
       </c>
       <c r="K26" s="0" t="s">
-        <v>416</v>
+        <v>532</v>
       </c>
     </row>
     <row r="27">
@@ -2865,19 +3081,19 @@
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>461</v>
+        <v>521</v>
       </c>
       <c r="B28" s="0">
-        <v>648</v>
+        <v>801</v>
       </c>
       <c r="C28" s="0">
-        <v>1374</v>
+        <v>1407</v>
       </c>
       <c r="D28" s="0">
-        <v>1297</v>
+        <v>1158</v>
       </c>
       <c r="E28" s="0">
-        <v>1443</v>
+        <v>1404</v>
       </c>
       <c r="F28" s="0">
         <v>2160</v>
@@ -2889,13 +3105,13 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>462</v>
+        <v>522</v>
       </c>
       <c r="J28" s="0" t="s">
-        <v>463</v>
+        <v>523</v>
       </c>
       <c r="K28" s="0" t="s">
-        <v>464</v>
+        <v>524</v>
       </c>
     </row>
     <row r="29">
@@ -2970,19 +3186,19 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>485</v>
+        <v>533</v>
       </c>
       <c r="B31" s="0">
-        <v>476</v>
+        <v>385</v>
       </c>
       <c r="C31" s="0">
-        <v>1568</v>
+        <v>1565</v>
       </c>
       <c r="D31" s="0">
-        <v>1334</v>
+        <v>1188</v>
       </c>
       <c r="E31" s="0">
-        <v>1608</v>
+        <v>1388</v>
       </c>
       <c r="F31" s="0">
         <v>2160</v>
@@ -2994,13 +3210,13 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>486</v>
+        <v>534</v>
       </c>
       <c r="J31" s="0" t="s">
-        <v>487</v>
+        <v>535</v>
       </c>
       <c r="K31" s="0" t="s">
-        <v>488</v>
+        <v>536</v>
       </c>
     </row>
   </sheetData>

--- a/config/acquisitionConfig/roi.csv.xlsx
+++ b/config/acquisitionConfig/roi.csv.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="649">
   <si>
     <t>Angle</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1795,6 +1795,198 @@
   </si>
   <si>
     <t>[950 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeMomentumCheck</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeMomentumCheck</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeMomentumCheck</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeBoBmTof8000</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>BMPDloopTof8000</t>
+  </si>
+  <si>
+    <t>[949 1271 160 145]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[950 100]</t>
+  </si>
+  <si>
+    <t>BMPDloopTof8000</t>
+  </si>
+  <si>
+    <t>[939 1271 160 145]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[950 100]</t>
+  </si>
+  <si>
+    <t>BMPDLoopFullBoTof8000</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>BMPDLoopFullBoTof8000</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>BMPDLoopFullBoTof8000</t>
+  </si>
+  <si>
+    <t>[926 1269 150 100]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[750 100]</t>
+  </si>
+  <si>
+    <t>BMPDLoopFullBoTof6000</t>
+  </si>
+  <si>
+    <t>[1100 1262 150 100]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[800 100]</t>
+  </si>
+  <si>
+    <t>BMPDLoopFullBoTof6000</t>
+  </si>
+  <si>
+    <t>[1049 1264 150 100]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[750 100]</t>
+  </si>
+  <si>
+    <t>BMPDLoopFullBoTof6000</t>
+  </si>
+  <si>
+    <t>[1049 1264 150 100]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[750 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeBoBmTof8000</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>BMPDLoopFullBoTof6000</t>
+  </si>
+  <si>
+    <t>[1099 1262 150 100]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[750 100]</t>
+  </si>
+  <si>
+    <t>BMPDLoopFullBoTof6000</t>
+  </si>
+  <si>
+    <t>[1069 1273 120 90]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[750 100]</t>
+  </si>
+  <si>
+    <t>BMPDLoopFullBoTof6000</t>
+  </si>
+  <si>
+    <t>[1099 1272 140 90]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[750 100]</t>
   </si>
 </sst>
 </file>
@@ -2121,7 +2313,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.85546875" customWidth="true"/>
@@ -2871,7 +3063,7 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="B22" s="0">
         <v>406</v>
@@ -2895,13 +3087,13 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>582</v>
+        <v>606</v>
       </c>
       <c r="J22" s="0" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="K22" s="0" t="s">
-        <v>584</v>
+        <v>608</v>
       </c>
     </row>
     <row r="23">
@@ -3217,6 +3409,146 @@
       </c>
       <c r="K31" s="0" t="s">
         <v>536</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="s">
+        <v>593</v>
+      </c>
+      <c r="B32" s="0">
+        <v>872</v>
+      </c>
+      <c r="C32" s="0">
+        <v>1178</v>
+      </c>
+      <c r="D32" s="0">
+        <v>1163</v>
+      </c>
+      <c r="E32" s="0">
+        <v>1443</v>
+      </c>
+      <c r="F32" s="0">
+        <v>2160</v>
+      </c>
+      <c r="G32" s="0">
+        <v>2560</v>
+      </c>
+      <c r="H32" s="0">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I32" s="0" t="s">
+        <v>594</v>
+      </c>
+      <c r="J32" s="0" t="s">
+        <v>595</v>
+      </c>
+      <c r="K32" s="0" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="s">
+        <v>633</v>
+      </c>
+      <c r="B33" s="0">
+        <v>331</v>
+      </c>
+      <c r="C33" s="0">
+        <v>2099</v>
+      </c>
+      <c r="D33" s="0">
+        <v>1224</v>
+      </c>
+      <c r="E33" s="0">
+        <v>1374</v>
+      </c>
+      <c r="F33" s="0">
+        <v>2160</v>
+      </c>
+      <c r="G33" s="0">
+        <v>2560</v>
+      </c>
+      <c r="H33" s="0">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I33" s="0" t="s">
+        <v>634</v>
+      </c>
+      <c r="J33" s="0" t="s">
+        <v>635</v>
+      </c>
+      <c r="K33" s="0" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="s">
+        <v>617</v>
+      </c>
+      <c r="B34" s="0">
+        <v>441</v>
+      </c>
+      <c r="C34" s="0">
+        <v>1481</v>
+      </c>
+      <c r="D34" s="0">
+        <v>1203</v>
+      </c>
+      <c r="E34" s="0">
+        <v>1399</v>
+      </c>
+      <c r="F34" s="0">
+        <v>2160</v>
+      </c>
+      <c r="G34" s="0">
+        <v>2560</v>
+      </c>
+      <c r="H34" s="0">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I34" s="0" t="s">
+        <v>618</v>
+      </c>
+      <c r="J34" s="0" t="s">
+        <v>619</v>
+      </c>
+      <c r="K34" s="0" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="s">
+        <v>645</v>
+      </c>
+      <c r="B35" s="0">
+        <v>572</v>
+      </c>
+      <c r="C35" s="0">
+        <v>1652</v>
+      </c>
+      <c r="D35" s="0">
+        <v>1185</v>
+      </c>
+      <c r="E35" s="0">
+        <v>1423</v>
+      </c>
+      <c r="F35" s="0">
+        <v>2160</v>
+      </c>
+      <c r="G35" s="0">
+        <v>2560</v>
+      </c>
+      <c r="H35" s="0">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I35" s="0" t="s">
+        <v>646</v>
+      </c>
+      <c r="J35" s="0" t="s">
+        <v>647</v>
+      </c>
+      <c r="K35" s="0" t="s">
+        <v>648</v>
       </c>
     </row>
   </sheetData>

--- a/config/acquisitionConfig/roi.csv.xlsx
+++ b/config/acquisitionConfig/roi.csv.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="661">
   <si>
     <t>Angle</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1987,6 +1987,42 @@
   </si>
   <si>
     <t>[750 100]</t>
+  </si>
+  <si>
+    <t>BMPDLoopFullBoTof8000</t>
+  </si>
+  <si>
+    <t>[1229 1257 150 150]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[800 100]</t>
+  </si>
+  <si>
+    <t>BMPDLoopFullBoTof8000</t>
+  </si>
+  <si>
+    <t>[1229 1257 150 150]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[800 100]</t>
+  </si>
+  <si>
+    <t>BMPDLoopFullBoTof8000</t>
+  </si>
+  <si>
+    <t>[1229 1257 200 150]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[850 100]</t>
   </si>
 </sst>
 </file>
@@ -3483,19 +3519,19 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>617</v>
+        <v>657</v>
       </c>
       <c r="B34" s="0">
-        <v>441</v>
+        <v>674</v>
       </c>
       <c r="C34" s="0">
-        <v>1481</v>
+        <v>1880</v>
       </c>
       <c r="D34" s="0">
-        <v>1203</v>
+        <v>1161</v>
       </c>
       <c r="E34" s="0">
-        <v>1399</v>
+        <v>1451</v>
       </c>
       <c r="F34" s="0">
         <v>2160</v>
@@ -3507,13 +3543,13 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>618</v>
+        <v>658</v>
       </c>
       <c r="J34" s="0" t="s">
-        <v>619</v>
+        <v>659</v>
       </c>
       <c r="K34" s="0" t="s">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="35">

--- a/config/acquisitionConfig/roi.csv.xlsx
+++ b/config/acquisitionConfig/roi.csv.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="669">
   <si>
     <t>Angle</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2023,6 +2023,30 @@
   </si>
   <si>
     <t>[850 100]</t>
+  </si>
+  <si>
+    <t>BMPDloopTof8000CC</t>
+  </si>
+  <si>
+    <t>[950 1545 160 145]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[950 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeCCBoBmTof4000</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
   </si>
 </sst>
 </file>
@@ -2349,7 +2373,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.85546875" customWidth="true"/>
@@ -3587,6 +3611,76 @@
         <v>648</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>661</v>
+      </c>
+      <c r="B36" s="0">
+        <v>265</v>
+      </c>
+      <c r="C36" s="0">
+        <v>1727</v>
+      </c>
+      <c r="D36" s="0">
+        <v>1415</v>
+      </c>
+      <c r="E36" s="0">
+        <v>1713</v>
+      </c>
+      <c r="F36" s="0">
+        <v>2160</v>
+      </c>
+      <c r="G36" s="0">
+        <v>2560</v>
+      </c>
+      <c r="H36" s="0">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I36" s="0" t="s">
+        <v>662</v>
+      </c>
+      <c r="J36" s="0" t="s">
+        <v>663</v>
+      </c>
+      <c r="K36" s="0" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="s">
+        <v>665</v>
+      </c>
+      <c r="B37" s="0">
+        <v>749</v>
+      </c>
+      <c r="C37" s="0">
+        <v>1507</v>
+      </c>
+      <c r="D37" s="0">
+        <v>1240</v>
+      </c>
+      <c r="E37" s="0">
+        <v>1504</v>
+      </c>
+      <c r="F37" s="0">
+        <v>2160</v>
+      </c>
+      <c r="G37" s="0">
+        <v>2560</v>
+      </c>
+      <c r="H37" s="0">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I37" s="0" t="s">
+        <v>666</v>
+      </c>
+      <c r="J37" s="0" t="s">
+        <v>667</v>
+      </c>
+      <c r="K37" s="0" t="s">
+        <v>668</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/config/acquisitionConfig/roi.csv.xlsx
+++ b/config/acquisitionConfig/roi.csv.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scientist\Documents\MMUser\config\acquisitionConfig\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D14D9A-7459-4CAB-A3E7-5899F804AB94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4691EE28-B121-4A60-A84D-BB8BF3B74CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="49">
   <si>
     <t>Angle</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -82,6 +82,108 @@
   </si>
   <si>
     <t>ODT</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>ODT</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>BECTOF</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>BECTOF</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>LatticeInSitu</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>LatticeInSitu</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>BECTOFRotated</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>ODTROI</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>XLatticeROI</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
   </si>
 </sst>
 </file>
@@ -112,7 +214,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -120,12 +222,14 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -406,26 +510,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.42578125" customWidth="1"/>
-    <col min="2" max="2" width="3.140625" customWidth="1"/>
-    <col min="3" max="3" width="5.140625" customWidth="1"/>
-    <col min="4" max="4" width="4.140625" customWidth="1"/>
-    <col min="5" max="5" width="5.140625" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" customWidth="1"/>
-    <col min="8" max="8" width="6.28515625" customWidth="1"/>
-    <col min="9" max="9" width="16.85546875" customWidth="1"/>
-    <col min="10" max="10" width="19.42578125" customWidth="1"/>
-    <col min="11" max="11" width="16.85546875" customWidth="1"/>
-    <col min="12" max="12" width="3.140625" customWidth="1"/>
-    <col min="13" max="14" width="2.140625" customWidth="1"/>
-    <col min="15" max="16" width="4.140625" customWidth="1"/>
+    <col min="1" max="1" width="14.85546875" customWidth="true"/>
+    <col min="2" max="2" width="4.140625" customWidth="true"/>
+    <col min="3" max="3" width="5.140625" customWidth="true"/>
+    <col min="4" max="4" width="4.140625" customWidth="true"/>
+    <col min="5" max="5" width="5.140625" customWidth="true"/>
+    <col min="6" max="6" width="11.140625" customWidth="true"/>
+    <col min="7" max="7" width="11.28515625" customWidth="true"/>
+    <col min="8" max="8" width="6.28515625" customWidth="true"/>
+    <col min="9" max="9" width="16.85546875" customWidth="true"/>
+    <col min="10" max="10" width="19.42578125" customWidth="true"/>
+    <col min="11" max="11" width="16.85546875" customWidth="true"/>
+    <col min="12" max="12" width="3.140625" customWidth="true"/>
+    <col min="13" max="14" width="2.140625" customWidth="true"/>
+    <col min="15" max="16" width="4.140625" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -460,7 +564,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -489,13 +593,13 @@
         <v>11</v>
       </c>
       <c r="J2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -524,45 +628,220 @@
         <v>11</v>
       </c>
       <c r="J3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4">
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="0">
+        <v>80</v>
+      </c>
+      <c r="C4" s="0">
+        <v>435</v>
+      </c>
+      <c r="D4" s="0">
         <v>85</v>
       </c>
-      <c r="C4">
-        <v>440</v>
-      </c>
-      <c r="D4">
-        <v>80</v>
-      </c>
-      <c r="E4">
-        <v>435</v>
-      </c>
-      <c r="F4">
-        <v>512</v>
-      </c>
-      <c r="G4">
-        <v>512</v>
-      </c>
-      <c r="H4">
+      <c r="E4" s="0">
+        <v>430</v>
+      </c>
+      <c r="F4" s="0">
+        <v>512</v>
+      </c>
+      <c r="G4" s="0">
+        <v>512</v>
+      </c>
+      <c r="H4" s="0">
         <v>0</v>
       </c>
-      <c r="I4" t="s">
-        <v>11</v>
-      </c>
-      <c r="J4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K4" t="s">
-        <v>11</v>
+      <c r="I4" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="0">
+        <v>170</v>
+      </c>
+      <c r="C5" s="0">
+        <v>300</v>
+      </c>
+      <c r="D5" s="0">
+        <v>185</v>
+      </c>
+      <c r="E5" s="0">
+        <v>335</v>
+      </c>
+      <c r="F5" s="0">
+        <v>512</v>
+      </c>
+      <c r="G5" s="0">
+        <v>512</v>
+      </c>
+      <c r="H5" s="0">
+        <v>0</v>
+      </c>
+      <c r="I5" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="0" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="0">
+        <v>75</v>
+      </c>
+      <c r="C6" s="0">
+        <v>600</v>
+      </c>
+      <c r="D6" s="0">
+        <v>325</v>
+      </c>
+      <c r="E6" s="0">
+        <v>385</v>
+      </c>
+      <c r="F6" s="0">
+        <v>512</v>
+      </c>
+      <c r="G6" s="0">
+        <v>512</v>
+      </c>
+      <c r="H6" s="0">
+        <v>30.02</v>
+      </c>
+      <c r="I6" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" s="0" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="0">
+        <v>285</v>
+      </c>
+      <c r="C7" s="0">
+        <v>400</v>
+      </c>
+      <c r="D7" s="0">
+        <v>285</v>
+      </c>
+      <c r="E7" s="0">
+        <v>425</v>
+      </c>
+      <c r="F7" s="0">
+        <v>512</v>
+      </c>
+      <c r="G7" s="0">
+        <v>512</v>
+      </c>
+      <c r="H7" s="0">
+        <v>30.02</v>
+      </c>
+      <c r="I7" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" s="0" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="0">
+        <v>137</v>
+      </c>
+      <c r="C8" s="0">
+        <v>492</v>
+      </c>
+      <c r="D8" s="0">
+        <v>142</v>
+      </c>
+      <c r="E8" s="0">
+        <v>487</v>
+      </c>
+      <c r="F8" s="0">
+        <v>512</v>
+      </c>
+      <c r="G8" s="0">
+        <v>512</v>
+      </c>
+      <c r="H8" s="0">
+        <v>345.19999999999999</v>
+      </c>
+      <c r="I8" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="K8" s="0" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="0">
+        <v>307</v>
+      </c>
+      <c r="C9" s="0">
+        <v>372</v>
+      </c>
+      <c r="D9" s="0">
+        <v>94</v>
+      </c>
+      <c r="E9" s="0">
+        <v>605</v>
+      </c>
+      <c r="F9" s="0">
+        <v>512</v>
+      </c>
+      <c r="G9" s="0">
+        <v>512</v>
+      </c>
+      <c r="H9" s="0">
+        <v>29</v>
+      </c>
+      <c r="I9" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="J9" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="K9" s="0" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/config/acquisitionConfig/roi.csv.xlsx
+++ b/config/acquisitionConfig/roi.csv.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="717">
   <si>
     <t>Angle</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2047,6 +2047,150 @@
   </si>
   <si>
     <t>[100 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeCCBoBmTof4000</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeCCBoBmTof4000</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeCCBoBmTof4000</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeCCBoBmTof4000</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeCCBoBmTof4000</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeCCSdTof4000</t>
+  </si>
+  <si>
+    <t>[956 1339 150 150]</t>
+  </si>
+  <si>
+    <t>[3 1]</t>
+  </si>
+  <si>
+    <t>[250 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeCCBoBmTof4000</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeCCBoBmTof4000</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeCCBoBmTof4000</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeCCPdTof4000</t>
+  </si>
+  <si>
+    <t>[897 1313 120 120]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[600 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeCCPdTof4000</t>
+  </si>
+  <si>
+    <t>[856 1297 160 120]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[600 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeCCPdTof4000</t>
+  </si>
+  <si>
+    <t>[866 1296 160 120]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[600 100]</t>
   </si>
 </sst>
 </file>
@@ -2373,7 +2517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.85546875" customWidth="true"/>
@@ -3648,19 +3792,19 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>665</v>
+        <v>701</v>
       </c>
       <c r="B37" s="0">
-        <v>749</v>
+        <v>830</v>
       </c>
       <c r="C37" s="0">
-        <v>1507</v>
+        <v>1290</v>
       </c>
       <c r="D37" s="0">
-        <v>1240</v>
+        <v>1245</v>
       </c>
       <c r="E37" s="0">
-        <v>1504</v>
+        <v>1425</v>
       </c>
       <c r="F37" s="0">
         <v>2160</v>
@@ -3672,13 +3816,83 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>666</v>
+        <v>702</v>
       </c>
       <c r="J37" s="0" t="s">
-        <v>667</v>
+        <v>703</v>
       </c>
       <c r="K37" s="0" t="s">
-        <v>668</v>
+        <v>704</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="s">
+        <v>689</v>
+      </c>
+      <c r="B38" s="0">
+        <v>627</v>
+      </c>
+      <c r="C38" s="0">
+        <v>1397</v>
+      </c>
+      <c r="D38" s="0">
+        <v>1270</v>
+      </c>
+      <c r="E38" s="0">
+        <v>1492</v>
+      </c>
+      <c r="F38" s="0">
+        <v>2160</v>
+      </c>
+      <c r="G38" s="0">
+        <v>2560</v>
+      </c>
+      <c r="H38" s="0">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I38" s="0" t="s">
+        <v>690</v>
+      </c>
+      <c r="J38" s="0" t="s">
+        <v>691</v>
+      </c>
+      <c r="K38" s="0" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="s">
+        <v>713</v>
+      </c>
+      <c r="B39" s="0">
+        <v>500</v>
+      </c>
+      <c r="C39" s="0">
+        <v>1320</v>
+      </c>
+      <c r="D39" s="0">
+        <v>1215</v>
+      </c>
+      <c r="E39" s="0">
+        <v>1445</v>
+      </c>
+      <c r="F39" s="0">
+        <v>2160</v>
+      </c>
+      <c r="G39" s="0">
+        <v>2560</v>
+      </c>
+      <c r="H39" s="0">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I39" s="0" t="s">
+        <v>714</v>
+      </c>
+      <c r="J39" s="0" t="s">
+        <v>715</v>
+      </c>
+      <c r="K39" s="0" t="s">
+        <v>716</v>
       </c>
     </row>
   </sheetData>

--- a/config/acquisitionConfig/roi.csv.xlsx
+++ b/config/acquisitionConfig/roi.csv.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="757">
   <si>
     <t>Angle</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2191,6 +2191,126 @@
   </si>
   <si>
     <t>[600 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeCCFulBoPdTof4000</t>
+  </si>
+  <si>
+    <t>[1119 1286 160 120]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[500 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeCCFulBoPdTof4000</t>
+  </si>
+  <si>
+    <t>[1069 1288 160 120]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[500 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeCCFulBoPdTof4000</t>
+  </si>
+  <si>
+    <t>[1050 1289 160 120]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[400 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeCCFulBoPdTof4000</t>
+  </si>
+  <si>
+    <t>[950 1293 160 120]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[400 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeCCPd3Tof4000</t>
+  </si>
+  <si>
+    <t>[906 1295 160 120]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[550 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeCCPdP5Tof4000</t>
+  </si>
+  <si>
+    <t>[932 1293 160 120]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[500 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeCCSdTof4000</t>
+  </si>
+  <si>
+    <t>[954 1289 150 150]</t>
+  </si>
+  <si>
+    <t>[3 1]</t>
+  </si>
+  <si>
+    <t>[250 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeCCPdP5Tof4000</t>
+  </si>
+  <si>
+    <t>[952 1293 160 120]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[500 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeCCPdTof4000Hold14</t>
+  </si>
+  <si>
+    <t>[899 1295 160 120]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[650 100]</t>
+  </si>
+  <si>
+    <t>NiLatticeCCPdTof4000Hold14</t>
+  </si>
+  <si>
+    <t>[899 1305 160 120]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[650 100]</t>
   </si>
 </sst>
 </file>
@@ -2517,10 +2637,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="25.85546875" customWidth="true"/>
+    <col min="1" max="1" width="26.5703125" customWidth="true"/>
     <col min="2" max="2" width="5.140625" customWidth="true"/>
     <col min="6" max="6" width="11.140625" customWidth="true"/>
     <col min="7" max="7" width="11.28515625" customWidth="true"/>
@@ -3827,19 +3947,19 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>689</v>
+        <v>741</v>
       </c>
       <c r="B38" s="0">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="C38" s="0">
-        <v>1397</v>
+        <v>1390</v>
       </c>
       <c r="D38" s="0">
-        <v>1270</v>
+        <v>1207</v>
       </c>
       <c r="E38" s="0">
-        <v>1492</v>
+        <v>1447</v>
       </c>
       <c r="F38" s="0">
         <v>2160</v>
@@ -3851,13 +3971,13 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>690</v>
+        <v>742</v>
       </c>
       <c r="J38" s="0" t="s">
-        <v>691</v>
+        <v>743</v>
       </c>
       <c r="K38" s="0" t="s">
-        <v>692</v>
+        <v>744</v>
       </c>
     </row>
     <row r="39">
@@ -3893,6 +4013,146 @@
       </c>
       <c r="K39" s="0" t="s">
         <v>716</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="s">
+        <v>729</v>
+      </c>
+      <c r="B40" s="0">
+        <v>673</v>
+      </c>
+      <c r="C40" s="0">
+        <v>1345</v>
+      </c>
+      <c r="D40" s="0">
+        <v>1233</v>
+      </c>
+      <c r="E40" s="0">
+        <v>1427</v>
+      </c>
+      <c r="F40" s="0">
+        <v>2160</v>
+      </c>
+      <c r="G40" s="0">
+        <v>2560</v>
+      </c>
+      <c r="H40" s="0">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I40" s="0" t="s">
+        <v>730</v>
+      </c>
+      <c r="J40" s="0" t="s">
+        <v>731</v>
+      </c>
+      <c r="K40" s="0" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>733</v>
+      </c>
+      <c r="B41" s="0">
+        <v>577</v>
+      </c>
+      <c r="C41" s="0">
+        <v>1345</v>
+      </c>
+      <c r="D41" s="0">
+        <v>1242</v>
+      </c>
+      <c r="E41" s="0">
+        <v>1420</v>
+      </c>
+      <c r="F41" s="0">
+        <v>2160</v>
+      </c>
+      <c r="G41" s="0">
+        <v>2560</v>
+      </c>
+      <c r="H41" s="0">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I41" s="0" t="s">
+        <v>734</v>
+      </c>
+      <c r="J41" s="0" t="s">
+        <v>735</v>
+      </c>
+      <c r="K41" s="0" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="s">
+        <v>745</v>
+      </c>
+      <c r="B42" s="0">
+        <v>500</v>
+      </c>
+      <c r="C42" s="0">
+        <v>1520</v>
+      </c>
+      <c r="D42" s="0">
+        <v>1215</v>
+      </c>
+      <c r="E42" s="0">
+        <v>1445</v>
+      </c>
+      <c r="F42" s="0">
+        <v>2160</v>
+      </c>
+      <c r="G42" s="0">
+        <v>2560</v>
+      </c>
+      <c r="H42" s="0">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I42" s="0" t="s">
+        <v>746</v>
+      </c>
+      <c r="J42" s="0" t="s">
+        <v>747</v>
+      </c>
+      <c r="K42" s="0" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="s">
+        <v>753</v>
+      </c>
+      <c r="B43" s="0">
+        <v>488</v>
+      </c>
+      <c r="C43" s="0">
+        <v>1394</v>
+      </c>
+      <c r="D43" s="0">
+        <v>1235</v>
+      </c>
+      <c r="E43" s="0">
+        <v>1441</v>
+      </c>
+      <c r="F43" s="0">
+        <v>2160</v>
+      </c>
+      <c r="G43" s="0">
+        <v>2560</v>
+      </c>
+      <c r="H43" s="0">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I43" s="0" t="s">
+        <v>754</v>
+      </c>
+      <c r="J43" s="0" t="s">
+        <v>755</v>
+      </c>
+      <c r="K43" s="0" t="s">
+        <v>756</v>
       </c>
     </row>
   </sheetData>

--- a/config/acquisitionConfig/roi.csv.xlsx
+++ b/config/acquisitionConfig/roi.csv.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="69">
   <si>
     <t>Angle</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -175,6 +175,66 @@
   </si>
   <si>
     <t>XLatticeROI</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>BECROI2</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>BECROI2</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>Dichotomy05</t>
+  </si>
+  <si>
+    <t>[248 267 40 50]</t>
+  </si>
+  <si>
+    <t>[2 1]</t>
+  </si>
+  <si>
+    <t>[70 1]</t>
+  </si>
+  <si>
+    <t>ODTRotated</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>RMROI</t>
   </si>
   <si>
     <t>[]</t>
@@ -510,7 +570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.85546875" customWidth="true"/>
@@ -844,6 +904,146 @@
         <v>48</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="0">
+        <v>268</v>
+      </c>
+      <c r="C10" s="0">
+        <v>405</v>
+      </c>
+      <c r="D10" s="0">
+        <v>287</v>
+      </c>
+      <c r="E10" s="0">
+        <v>425</v>
+      </c>
+      <c r="F10" s="0">
+        <v>512</v>
+      </c>
+      <c r="G10" s="0">
+        <v>512</v>
+      </c>
+      <c r="H10" s="0">
+        <v>30.02</v>
+      </c>
+      <c r="I10" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="J10" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="K10" s="0" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="0">
+        <v>75</v>
+      </c>
+      <c r="C11" s="0">
+        <v>600</v>
+      </c>
+      <c r="D11" s="0">
+        <v>325</v>
+      </c>
+      <c r="E11" s="0">
+        <v>385</v>
+      </c>
+      <c r="F11" s="0">
+        <v>512</v>
+      </c>
+      <c r="G11" s="0">
+        <v>512</v>
+      </c>
+      <c r="H11" s="0">
+        <v>30.02</v>
+      </c>
+      <c r="I11" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="J11" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="K11" s="0" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="0">
+        <v>138</v>
+      </c>
+      <c r="C12" s="0">
+        <v>493</v>
+      </c>
+      <c r="D12" s="0">
+        <v>143</v>
+      </c>
+      <c r="E12" s="0">
+        <v>488</v>
+      </c>
+      <c r="F12" s="0">
+        <v>512</v>
+      </c>
+      <c r="G12" s="0">
+        <v>512</v>
+      </c>
+      <c r="H12" s="0">
+        <v>345</v>
+      </c>
+      <c r="I12" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="J12" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="K12" s="0" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="0">
+        <v>1</v>
+      </c>
+      <c r="C13" s="0">
+        <v>500</v>
+      </c>
+      <c r="D13" s="0">
+        <v>1</v>
+      </c>
+      <c r="E13" s="0">
+        <v>512</v>
+      </c>
+      <c r="F13" s="0">
+        <v>512</v>
+      </c>
+      <c r="G13" s="0">
+        <v>512</v>
+      </c>
+      <c r="H13" s="0">
+        <v>0</v>
+      </c>
+      <c r="I13" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="J13" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="K13" s="0" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/config/acquisitionConfig/roi.csv.xlsx
+++ b/config/acquisitionConfig/roi.csv.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="73">
   <si>
     <t>Angle</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -235,6 +235,18 @@
   </si>
   <si>
     <t>RMROI</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>RemoveBottomROI</t>
   </si>
   <si>
     <t>[]</t>
@@ -570,10 +582,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" customWidth="true"/>
+    <col min="1" max="1" width="18.140625" customWidth="true"/>
     <col min="2" max="2" width="4.140625" customWidth="true"/>
     <col min="3" max="3" width="5.140625" customWidth="true"/>
     <col min="4" max="4" width="4.140625" customWidth="true"/>
@@ -1044,6 +1056,41 @@
         <v>68</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" s="0">
+        <v>1</v>
+      </c>
+      <c r="C14" s="0">
+        <v>500</v>
+      </c>
+      <c r="D14" s="0">
+        <v>1</v>
+      </c>
+      <c r="E14" s="0">
+        <v>512</v>
+      </c>
+      <c r="F14" s="0">
+        <v>512</v>
+      </c>
+      <c r="G14" s="0">
+        <v>512</v>
+      </c>
+      <c r="H14" s="0">
+        <v>0</v>
+      </c>
+      <c r="I14" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="J14" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="K14" s="0" t="s">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/config/acquisitionConfig/roi.csv.xlsx
+++ b/config/acquisitionConfig/roi.csv.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="757">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="765">
   <si>
     <t>Angle</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2311,6 +2311,30 @@
   </si>
   <si>
     <t>[650 100]</t>
+  </si>
+  <si>
+    <t>NiLattice10MHzGwCavity</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
+  </si>
+  <si>
+    <t>NiLattice10MHzGwCavity</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[1 1]</t>
+  </si>
+  <si>
+    <t>[100 100]</t>
   </si>
 </sst>
 </file>
@@ -2637,7 +2661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.5703125" customWidth="true"/>
@@ -4155,6 +4179,41 @@
         <v>756</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="0" t="s">
+        <v>761</v>
+      </c>
+      <c r="B44" s="0">
+        <v>1050</v>
+      </c>
+      <c r="C44" s="0">
+        <v>1450</v>
+      </c>
+      <c r="D44" s="0">
+        <v>1260</v>
+      </c>
+      <c r="E44" s="0">
+        <v>1350</v>
+      </c>
+      <c r="F44" s="0">
+        <v>2160</v>
+      </c>
+      <c r="G44" s="0">
+        <v>2560</v>
+      </c>
+      <c r="H44" s="0">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I44" s="0" t="s">
+        <v>762</v>
+      </c>
+      <c r="J44" s="0" t="s">
+        <v>763</v>
+      </c>
+      <c r="K44" s="0" t="s">
+        <v>764</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
